--- a/survey_templates/034_water_supply_drill_feedback_survey--survey_templates.xlsx
+++ b/survey_templates/034_water_supply_drill_feedback_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_poor'}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very Poor'}</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Very Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'north'}</t>
+          <t>north</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'North'}</t>
+          <t>North</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'south'}</t>
+          <t>south</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'South'}</t>
+          <t>South</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'east'}</t>
+          <t>east</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'East'}</t>
+          <t>East</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'west'}</t>
+          <t>west</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'West'}</t>
+          <t>West</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'well'}</t>
+          <t>well</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Well'}</t>
+          <t>Well</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'stream'}</t>
+          <t>stream</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Stream'}</t>
+          <t>Stream</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'reservoir'}</t>
+          <t>reservoir</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Reservoir'}</t>
+          <t>Reservoir</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'very_poor'}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Very Poor'}</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'very_likely'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Very Likely'}</t>
+          <t>Very Likely</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_likely'}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Likely'}</t>
+          <t>Somewhat Likely</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'not_very_likely'}</t>
+          <t>not_very_likely</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Not Very Likely'}</t>
+          <t>Not Very Likely</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'not_somewhat_likely'}</t>
+          <t>not_somewhat_likely</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Not Somewhat Likely'}</t>
+          <t>Not Somewhat Likely</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'very_unlikely'}</t>
+          <t>very_unlikely</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Very Unlikely'}</t>
+          <t>Very Unlikely</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'very_likely'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Very Likely'}</t>
+          <t>Very Likely</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_likely'}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Likely'}</t>
+          <t>Somewhat Likely</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'not_very_likely'}</t>
+          <t>not_very_likely</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Not Very Likely'}</t>
+          <t>Not Very Likely</t>
         </is>
       </c>
     </row>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'not_somewhat_likely'}</t>
+          <t>not_somewhat_likely</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Not Somewhat Likely'}</t>
+          <t>Not Somewhat Likely</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'very_likely'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Very Likely'}</t>
+          <t>Very Likely</t>
         </is>
       </c>
     </row>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_likely'}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Likely'}</t>
+          <t>Somewhat Likely</t>
         </is>
       </c>
     </row>
@@ -1479,12 +1479,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'not_very_likely'}</t>
+          <t>not_very_likely</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Not Very Likely'}</t>
+          <t>Not Very Likely</t>
         </is>
       </c>
     </row>
@@ -1496,12 +1496,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'not_somewhat_likely'}</t>
+          <t>not_somewhat_likely</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Not Somewhat Likely'}</t>
+          <t>Not Somewhat Likely</t>
         </is>
       </c>
     </row>
